--- a/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_DAN_BOUNDARY_GUARDRAILS_BACKUP.xlsx
+++ b/KURIKULUM2026_REVISI/043_MATRIKS_CPL_CPMK_BoK_DAN_BOUNDARY_GUARDRAILS_BACKUP.xlsx
@@ -9045,7 +9045,7 @@
     <row r="440" ht="16" customHeight="1">
       <c r="A440" s="7" t="inlineStr">
         <is>
-          <t>`STI-624`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="B440" s="7" t="inlineStr">
@@ -9082,7 +9082,7 @@
     <row r="441" ht="16" customHeight="1">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>`STI-625`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -9119,7 +9119,7 @@
     <row r="442" ht="16" customHeight="1">
       <c r="A442" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`</t>
+          <t>`STI-726`</t>
         </is>
       </c>
       <c r="B442" s="7" t="inlineStr">
@@ -9156,7 +9156,7 @@
     <row r="443" ht="16" customHeight="1">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>`STI-627`</t>
+          <t>`STI-727`</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -9194,7 +9194,7 @@
     <row r="445" ht="20" customHeight="1">
       <c r="A445" s="3" t="inlineStr">
         <is>
-          <t>STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B445" s="4" t="n"/>
@@ -9317,7 +9317,7 @@
     <row r="452" ht="20" customHeight="1">
       <c r="A452" s="3" t="inlineStr">
         <is>
-          <t>STI-624 — Integrasi Layanan Cerdas Berbasis AI</t>
+          <t>STI-726 — Integrasi Layanan Cerdas Berbasis AI</t>
         </is>
       </c>
       <c r="B452" s="4" t="n"/>
@@ -9528,7 +9528,7 @@
     <row r="463" ht="20" customHeight="1">
       <c r="A463" s="3" t="inlineStr">
         <is>
-          <t>STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B463" s="4" t="n"/>
@@ -9651,7 +9651,7 @@
     <row r="470" ht="20" customHeight="1">
       <c r="A470" s="3" t="inlineStr">
         <is>
-          <t>STI-625 — Smart City &amp; Pemerintahan Digital</t>
+          <t>STI-727 — Smart City &amp; Pemerintahan Digital</t>
         </is>
       </c>
       <c r="B470" s="4" t="n"/>
@@ -9862,7 +9862,7 @@
     <row r="481" ht="20" customHeight="1">
       <c r="A481" s="3" t="inlineStr">
         <is>
-          <t>STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B481" s="4" t="n"/>
@@ -9985,7 +9985,7 @@
     <row r="488" ht="20" customHeight="1">
       <c r="A488" s="3" t="inlineStr">
         <is>
-          <t>STI-626 — Deep Learning &amp; Neural Networks</t>
+          <t>STI-726 — Deep Learning &amp; Neural Networks</t>
         </is>
       </c>
       <c r="B488" s="4" t="n"/>
@@ -10196,7 +10196,7 @@
     <row r="499" ht="20" customHeight="1">
       <c r="A499" s="3" t="inlineStr">
         <is>
-          <t>STI-627 — Digital Platform Engineering</t>
+          <t>STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B499" s="4" t="n"/>
@@ -10319,7 +10319,7 @@
     <row r="506" ht="20" customHeight="1">
       <c r="A506" s="3" t="inlineStr">
         <is>
-          <t>STI-627 — Digital Platform Engineering</t>
+          <t>STI-727 — Digital Platform Engineering</t>
         </is>
       </c>
       <c r="B506" s="4" t="n"/>
@@ -10595,7 +10595,7 @@
       </c>
       <c r="D519" s="7" t="inlineStr">
         <is>
-          <t>`STI-627`, `MKU-204`</t>
+          <t>`STI-727`, `MKU-204`</t>
         </is>
       </c>
       <c r="E519" s="7" t="inlineStr">
@@ -14064,7 +14064,7 @@
       </c>
       <c r="E697" s="7" t="inlineStr">
         <is>
-          <t>`STI-413`, `STI-624` Integrasi AI</t>
+          <t>`STI-413`, `STI-726` Integrasi AI</t>
         </is>
       </c>
       <c r="F697" s="7" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="E699" s="7" t="inlineStr">
         <is>
-          <t>`STI-626`, `STI-521` IoT</t>
+          <t>`STI-726`, `STI-521` IoT</t>
         </is>
       </c>
       <c r="F699" s="7" t="inlineStr">
